--- a/palabras_arg_rev.xlsx
+++ b/palabras_arg_rev.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/soledadaraya/Library/CloudStorage/Dropbox/Lucía Miranda Fondecyt/femocratas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A171B24C-520D-914B-84AE-C1783CC24B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5297FDE7-B0D8-8D43-A021-4A5404506482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4236,6 +4236,9 @@
       <c r="B128">
         <v>11</v>
       </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
@@ -4546,6 +4549,9 @@
       </c>
       <c r="B165">
         <v>387</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
